--- a/benchmarks/attachment_intelligence/fixtures/files/f01.xlsx
+++ b/benchmarks/attachment_intelligence/fixtures/files/f01.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Шайба M12</t>
+          <t xml:space="preserve">Шайба DIN125 M12 цинк</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
